--- a/truck_loading.xlsx
+++ b/truck_loading.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gustavo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gustavo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BDE2A8-663E-41DA-9E56-AE6B42C4A5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B222A88-4E41-44F3-918B-BAD93A9964E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{87E41F67-8598-469E-8D95-6B4D217A0F10}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{87E41F67-8598-469E-8D95-6B4D217A0F10}"/>
   </bookViews>
   <sheets>
     <sheet name="Order" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -47,6 +47,13 @@
   </si>
   <si>
     <t>SEVEL</t>
+  </si>
+  <si>
+    <t>Cliente 149
+Causale 18</t>
+  </si>
+  <si>
+    <t>PRESSE MIRAFIORI SPEDIZIONI</t>
   </si>
   <si>
     <t>Container</t>
@@ -86,22 +93,6 @@
   </si>
   <si>
     <t>TRACTOR</t>
-  </si>
-  <si>
-    <t>PRESSE SPEDIZIONI</t>
-  </si>
-  <si>
-    <t>Cliente X
-Causale Y</t>
-  </si>
-  <si>
-    <t>X/X/20XX</t>
-  </si>
-  <si>
-    <t>Automotive Industry</t>
-  </si>
-  <si>
-    <t>TIER 1</t>
   </si>
 </sst>
 </file>
@@ -495,6 +486,243 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>143138</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>325981</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>97165</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Immagine 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{290FAA79-A46A-422C-BA11-6A790195515A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="141233" y="0"/>
+          <a:ext cx="1925918" cy="605800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>143138</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>21430</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>97165</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Immagine 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3C11F24-83F9-45E9-8725-21394E6CB95A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="141233" y="0"/>
+          <a:ext cx="1918298" cy="601990"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>143138</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>455356</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>93355</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Immagine 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{276B57D7-3F22-4901-8DD7-40CCB5B8C71C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="143138" y="0"/>
+          <a:ext cx="1934082" cy="606344"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -830,9 +1058,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="5" t="s">
@@ -856,19 +1082,17 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="14" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G2" s="15"/>
-      <c r="H2" s="17" t="s">
-        <v>18</v>
+      <c r="H2" s="17">
+        <v>45078</v>
       </c>
       <c r="I2" s="18"/>
       <c r="J2" s="19"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="23"/>
       <c r="D3" s="10"/>
@@ -881,7 +1105,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
@@ -895,10 +1119,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1097,6 +1321,7 @@
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1118,9 +1343,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="26"/>
@@ -1144,9 +1367,7 @@
       <c r="J2" s="18"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="11"/>
@@ -1159,7 +1380,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
@@ -1173,22 +1394,22 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1276,7 +1497,7 @@
         <v>7897</v>
       </c>
       <c r="B10">
-        <v>220</v>
+        <v>2200</v>
       </c>
       <c r="C10">
         <v>1100</v>
@@ -1376,7 +1597,7 @@
         <v>8648</v>
       </c>
       <c r="B15">
-        <v>240</v>
+        <v>2400</v>
       </c>
       <c r="C15">
         <v>1200</v>
@@ -1416,10 +1637,10 @@
         <v>8786</v>
       </c>
       <c r="B17">
+        <v>2250</v>
+      </c>
+      <c r="C17">
         <v>1200</v>
-      </c>
-      <c r="C17">
-        <v>2250</v>
       </c>
       <c r="D17">
         <v>1300</v>
@@ -1443,6 +1664,7 @@
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1464,9 +1686,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="5"/>
@@ -1490,9 +1710,7 @@
       <c r="J2" s="19"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="23"/>
       <c r="D3" s="10"/>
@@ -1505,7 +1723,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
@@ -1519,24 +1737,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>13600</v>
@@ -1553,7 +1771,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>13600</v>
@@ -1570,7 +1788,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>9000</v>
@@ -1597,5 +1815,6 @@
     <mergeCell ref="D1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>